--- a/agent_runs/manjidiwang/episodes/ep17/storyboard_index.xlsx
+++ b/agent_runs/manjidiwang/episodes/ep17/storyboard_index.xlsx
@@ -84,7 +84,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>夜色逼近废厂（，总时长：11秒，镜头数：3个）</t>
+          <t>夜色逼近废厂</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -132,7 +132,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>抢先下井（，总时长：11秒，镜头数：4个）</t>
+          <t>抢先下井</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -180,7 +180,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>地下室破门（，总时长：11秒，镜头数：5个）</t>
+          <t>地下室破门</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -228,7 +228,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>黑烟倒灌（，总时长：11秒，镜头数：4个）</t>
+          <t>黑烟倒灌</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -276,7 +276,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>铁柜证据（，总时长：10秒，镜头数：4个）</t>
+          <t>铁柜证据</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -324,7 +324,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>火场狂笑（，总时长：10秒，镜头数：4个）</t>
+          <t>火场狂笑</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -372,7 +372,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>火海归来（，总时长：11秒，镜头数：4个）</t>
+          <t>火海归来</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -420,7 +420,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>铁证收网（，总时长：10秒，镜头数：4个）</t>
+          <t>铁证收网</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
